--- a/corr_matrix/residual_exam3A_1PL.xlsx
+++ b/corr_matrix/residual_exam3A_1PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>3A01</t>
@@ -525,52 +530,52 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1742207937797985</v>
+        <v>-0.1742363737884445</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01507072508541525</v>
+        <v>0.01507653259840354</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03397074104750416</v>
+        <v>-0.03395831933506984</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1863982503833811</v>
+        <v>-0.1864042577554356</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1242239274136901</v>
+        <v>0.1241901148701422</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1172543829627106</v>
+        <v>0.1172311112247121</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05690724990365823</v>
+        <v>0.05690515968485776</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.02128819822047352</v>
+        <v>-0.02128396091645484</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.08141410062702187</v>
+        <v>-0.08138680309434772</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08177604486232175</v>
+        <v>0.08174723940077358</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04581626449864236</v>
+        <v>-0.04580140958147292</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1363701728842386</v>
+        <v>-0.1363781593228737</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0859072678169138</v>
+        <v>-0.08588747540469145</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.06904480083364965</v>
+        <v>-0.06902181566263875</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2385553216662413</v>
+        <v>0.2385784067744992</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.05405983917825068</v>
+        <v>-0.0540390569466519</v>
       </c>
     </row>
     <row r="3">
@@ -580,55 +585,55 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1742207937797985</v>
+        <v>-0.1742363737884445</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08328085838896297</v>
+        <v>0.08330173101255579</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1736306941311984</v>
+        <v>0.173639487701153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01202975474830164</v>
+        <v>0.01203161718028463</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2007197165391434</v>
+        <v>-0.2007123235501445</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2961833904967521</v>
+        <v>-0.2961864056284811</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1383455245518846</v>
+        <v>-0.1383163717022138</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.05400399832096074</v>
+        <v>-0.05399433163084887</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02340326578092856</v>
+        <v>0.02340227911674168</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.04808303121819794</v>
+        <v>-0.04807039596301699</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1201545696330645</v>
+        <v>0.1201567064877766</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1207965287490984</v>
+        <v>-0.1207863665845473</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.07624482111592684</v>
+        <v>-0.07624160387848315</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2013233581676131</v>
+        <v>-0.2013189267638788</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2856321845897071</v>
+        <v>-0.2856150608309959</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01665625854247623</v>
+        <v>0.01666186926508546</v>
       </c>
     </row>
     <row r="4">
@@ -638,55 +643,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01507072508541525</v>
+        <v>0.01507653259840354</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08328085838896297</v>
+        <v>0.08330173101255579</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2274382907650001</v>
+        <v>0.2274410962724597</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08574469293129384</v>
+        <v>-0.08573283767195616</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01262855831049351</v>
+        <v>0.01264634897865603</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2449906846750936</v>
+        <v>-0.2450005351455194</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06622231339408313</v>
+        <v>-0.06622079020550126</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.01729296421260009</v>
+        <v>-0.01730439750735322</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007164311395986928</v>
+        <v>0.007146367729524723</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09592637468584336</v>
+        <v>0.09594720649880781</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08916779336836048</v>
+        <v>-0.08916906579002487</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04003275650023442</v>
+        <v>0.04003962300595093</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2801606259435531</v>
+        <v>-0.2801659107280428</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2573427440388361</v>
+        <v>-0.2573533126466964</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2489369253156401</v>
+        <v>-0.2489262478488573</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1334469483901256</v>
+        <v>-0.1334446568452315</v>
       </c>
     </row>
     <row r="5">
@@ -696,55 +701,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.03397074104750416</v>
+        <v>-0.03395831933506984</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1736306941311984</v>
+        <v>0.173639487701153</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2274382907650001</v>
+        <v>0.2274410962724597</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1844747526983143</v>
+        <v>-0.1844499587422991</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.05392902225899207</v>
+        <v>-0.05391991912747766</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1030668914596956</v>
+        <v>-0.1030838219932819</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3220821005155343</v>
+        <v>-0.3220989245872536</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2563838000966476</v>
+        <v>0.2563564572980592</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07683843226577312</v>
+        <v>0.07680517892098498</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03131983604658766</v>
+        <v>0.03133011328846458</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03063784265424613</v>
+        <v>-0.03066024979795064</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1898782187729637</v>
+        <v>-0.1898648785834949</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2134331203135311</v>
+        <v>-0.213438523568853</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.205213775179221</v>
+        <v>-0.205251616984405</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2016406696038461</v>
+        <v>-0.2016478065199879</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.07209876631395257</v>
+        <v>-0.07210677558561417</v>
       </c>
     </row>
     <row r="6">
@@ -754,55 +759,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1863982503833811</v>
+        <v>-0.1864042577554356</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01202975474830164</v>
+        <v>0.01203161718028463</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08574469293129384</v>
+        <v>-0.08573283767195616</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1844747526983143</v>
+        <v>-0.1844499587422991</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05634792585374802</v>
+        <v>0.05635486430193522</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.06397909619967831</v>
+        <v>-0.06398003233713716</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2003744911882011</v>
+        <v>-0.2003778816407986</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2893657396013423</v>
+        <v>-0.2893645052131426</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.08682848184069122</v>
+        <v>-0.08679154846078134</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06682621765704194</v>
+        <v>0.06682582247946446</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1674551648904312</v>
+        <v>-0.1674223281053749</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1116100843599213</v>
+        <v>0.1115976232155826</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.02685869375093614</v>
+        <v>-0.02683841999411802</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2839238188430767</v>
+        <v>-0.2839049258083452</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3191799752794228</v>
+        <v>-0.3191443600895812</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.01837612761457592</v>
+        <v>-0.01835019132009135</v>
       </c>
     </row>
     <row r="7">
@@ -812,55 +817,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1242239274136901</v>
+        <v>0.1241901148701422</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2007197165391434</v>
+        <v>-0.2007123235501445</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01262855831049351</v>
+        <v>0.01264634897865603</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.05392902225899207</v>
+        <v>-0.05391991912747766</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05634792585374802</v>
+        <v>0.05635486430193522</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2297333409473516</v>
+        <v>0.2297098446372762</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1380553433917251</v>
+        <v>-0.1380474763794478</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2479121357588424</v>
+        <v>-0.2479218511189953</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1497985283406335</v>
+        <v>-0.149786326329071</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.07235548787288949</v>
+        <v>-0.07237539914311558</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07996470888604638</v>
+        <v>-0.07995701245830629</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.001968247847741664</v>
+        <v>-0.001958155407679934</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.03634221234000056</v>
+        <v>-0.03632304629207472</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1126902402387405</v>
+        <v>-0.1126794381419477</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.09661437986647123</v>
+        <v>0.09663939489526456</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1196309482847191</v>
+        <v>-0.1196118101964955</v>
       </c>
     </row>
     <row r="8">
@@ -870,55 +875,55 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1172543829627106</v>
+        <v>0.1172311112247121</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2961833904967521</v>
+        <v>-0.2961864056284811</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2449906846750936</v>
+        <v>-0.2450005351455194</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1030668914596956</v>
+        <v>-0.1030838219932819</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.06397909619967831</v>
+        <v>-0.06398003233713716</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2297333409473516</v>
+        <v>0.2297098446372762</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08199613172322644</v>
+        <v>0.08199565546993313</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.03610316771539913</v>
+        <v>-0.03611737679524007</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01213528230597984</v>
+        <v>0.01213072816512191</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.138006667562127</v>
+        <v>-0.1380365463148818</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1297369518057461</v>
+        <v>-0.129755530082586</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06365900865791643</v>
+        <v>-0.06364291985492512</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.02758017770280991</v>
+        <v>-0.02757330756539884</v>
       </c>
       <c r="P8" t="n">
-        <v>0.06998007005675233</v>
+        <v>0.06997282380626559</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.08893520048610355</v>
+        <v>0.08893469340784468</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02723473760500227</v>
+        <v>0.02723415946797429</v>
       </c>
     </row>
     <row r="9">
@@ -928,55 +933,55 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05690724990365823</v>
+        <v>0.05690515968485776</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1383455245518846</v>
+        <v>-0.1383163717022138</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06622231339408313</v>
+        <v>-0.06622079020550126</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3220821005155343</v>
+        <v>-0.3220989245872536</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2003744911882011</v>
+        <v>-0.2003778816407986</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1380553433917251</v>
+        <v>-0.1380474763794478</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08199613172322644</v>
+        <v>0.08199565546993313</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2115361303113784</v>
+        <v>0.2115350652816519</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1740472608691041</v>
+        <v>0.1740128763238641</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2060422782647531</v>
+        <v>-0.2060310539659185</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1952748602560186</v>
+        <v>-0.1953031515581428</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0339971375751135</v>
+        <v>-0.03397103477329744</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04342372201805725</v>
+        <v>0.04340174983314189</v>
       </c>
       <c r="P9" t="n">
-        <v>0.124079746024738</v>
+        <v>0.124056244371458</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09159705332043251</v>
+        <v>0.09157803497197814</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.1366922402025685</v>
+        <v>-0.1367166683597793</v>
       </c>
     </row>
     <row r="10">
@@ -986,55 +991,55 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.02128819822047352</v>
+        <v>-0.02128396091645484</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.05400399832096074</v>
+        <v>-0.05399433163084887</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.01729296421260009</v>
+        <v>-0.01730439750735322</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2563838000966476</v>
+        <v>0.2563564572980592</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2893657396013423</v>
+        <v>-0.2893645052131426</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2479121357588424</v>
+        <v>-0.2479218511189953</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.03610316771539913</v>
+        <v>-0.03611737679524007</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2115361303113784</v>
+        <v>0.2115350652816519</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04903790496709102</v>
+        <v>0.04899300212403422</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.09644205966893776</v>
+        <v>-0.09644786817326328</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1567833623138591</v>
+        <v>-0.1568283901972255</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02533536985882069</v>
+        <v>-0.02530587189577745</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.06579511969946349</v>
+        <v>-0.06581230433638185</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1713143559026086</v>
+        <v>0.1712780086623092</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.16482181116206</v>
+        <v>-0.1648444999658344</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.1053417684692502</v>
+        <v>-0.1053678463581126</v>
       </c>
     </row>
     <row r="11">
@@ -1044,55 +1049,55 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.08141410062702187</v>
+        <v>-0.08138680309434772</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02340326578092856</v>
+        <v>0.02340227911674168</v>
       </c>
       <c r="D11" t="n">
-        <v>0.007164311395986928</v>
+        <v>0.007146367729524723</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07683843226577312</v>
+        <v>0.07680517892098498</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08682848184069122</v>
+        <v>-0.08679154846078134</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1497985283406335</v>
+        <v>-0.149786326329071</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01213528230597984</v>
+        <v>0.01213072816512191</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1740472608691041</v>
+        <v>0.1740128763238641</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04903790496709102</v>
+        <v>0.04899300212403422</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.09432258865422592</v>
+        <v>-0.09431606208944276</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.00119945554474548</v>
+        <v>-0.001233035740072205</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1016934558854444</v>
+        <v>-0.1016711038087321</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2854086051357521</v>
+        <v>-0.2854224890833403</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1606303868978582</v>
+        <v>-0.1606870530328374</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.09964985837325757</v>
+        <v>-0.09967136712906929</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.2121871143928384</v>
+        <v>-0.212209981122964</v>
       </c>
     </row>
     <row r="12">
@@ -1102,55 +1107,55 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08177604486232175</v>
+        <v>0.08174723940077358</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.04808303121819794</v>
+        <v>-0.04807039596301699</v>
       </c>
       <c r="D12" t="n">
-        <v>0.09592637468584336</v>
+        <v>0.09594720649880781</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03131983604658766</v>
+        <v>0.03133011328846458</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06682621765704194</v>
+        <v>0.06682582247946446</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.07235548787288949</v>
+        <v>-0.07237539914311558</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.138006667562127</v>
+        <v>-0.1380365463148818</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2060422782647531</v>
+        <v>-0.2060310539659185</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.09644205966893776</v>
+        <v>-0.09644786817326328</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.09432258865422592</v>
+        <v>-0.09431606208944276</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1727028604834785</v>
+        <v>-0.1726990352675782</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.01005128345620031</v>
+        <v>-0.01004099517283491</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1142672004044944</v>
+        <v>0.1142779338330791</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2148822246209863</v>
+        <v>-0.2148776531625478</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1535565692291639</v>
+        <v>-0.1535368865708304</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.07797808616199489</v>
+        <v>-0.07796446988769261</v>
       </c>
     </row>
     <row r="13">
@@ -1160,55 +1165,55 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.04581626449864236</v>
+        <v>-0.04580140958147292</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1201545696330645</v>
+        <v>0.1201567064877766</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.08916779336836048</v>
+        <v>-0.08916906579002487</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.03063784265424613</v>
+        <v>-0.03066024979795064</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1674551648904312</v>
+        <v>-0.1674223281053749</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.07996470888604638</v>
+        <v>-0.07995701245830629</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1297369518057461</v>
+        <v>-0.129755530082586</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1952748602560186</v>
+        <v>-0.1953031515581428</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1567833623138591</v>
+        <v>-0.1568283901972255</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.00119945554474548</v>
+        <v>-0.001233035740072205</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1727028604834785</v>
+        <v>-0.1726990352675782</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2452783432958554</v>
+        <v>-0.2452607986261583</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1898412769445333</v>
+        <v>-0.1898415862295819</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1366015913251175</v>
+        <v>0.136572932472734</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1719026519760143</v>
+        <v>0.1719004039390848</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.03703553495467672</v>
+        <v>-0.03703934509560883</v>
       </c>
     </row>
     <row r="14">
@@ -1218,55 +1223,55 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.1363701728842386</v>
+        <v>-0.1363781593228737</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1207965287490984</v>
+        <v>-0.1207863665845473</v>
       </c>
       <c r="D14" t="n">
-        <v>0.04003275650023442</v>
+        <v>0.04003962300595093</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1898782187729637</v>
+        <v>-0.1898648785834949</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1116100843599213</v>
+        <v>0.1115976232155826</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.001968247847741664</v>
+        <v>-0.001958155407679934</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.06365900865791643</v>
+        <v>-0.06364291985492512</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0339971375751135</v>
+        <v>-0.03397103477329744</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.02533536985882069</v>
+        <v>-0.02530587189577745</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1016934558854444</v>
+        <v>-0.1016711038087321</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.01005128345620031</v>
+        <v>-0.01004099517283491</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2452783432958554</v>
+        <v>-0.2452607986261583</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01221413709102346</v>
+        <v>0.01221014908796429</v>
       </c>
       <c r="P14" t="n">
-        <v>0.04611701743477972</v>
+        <v>0.04613873483677771</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1962577232960025</v>
+        <v>-0.1962583371125046</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.2627404681404036</v>
+        <v>-0.2627390228657359</v>
       </c>
     </row>
     <row r="15">
@@ -1276,55 +1281,55 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0859072678169138</v>
+        <v>-0.08588747540469145</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.07624482111592684</v>
+        <v>-0.07624160387848315</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2801606259435531</v>
+        <v>-0.2801659107280428</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2134331203135311</v>
+        <v>-0.213438523568853</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.02685869375093614</v>
+        <v>-0.02683841999411802</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.03634221234000056</v>
+        <v>-0.03632304629207472</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02758017770280991</v>
+        <v>-0.02757330756539884</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04342372201805725</v>
+        <v>0.04340174983314189</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.06579511969946349</v>
+        <v>-0.06581230433638185</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2854086051357521</v>
+        <v>-0.2854224890833403</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1142672004044944</v>
+        <v>0.1142779338330791</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1898412769445333</v>
+        <v>-0.1898415862295819</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01221413709102346</v>
+        <v>0.01221014908796429</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.109614919639041</v>
+        <v>0.1096078040842981</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.07527496955582919</v>
+        <v>-0.07527595497036675</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.1390574325133239</v>
+        <v>-0.1390671331264856</v>
       </c>
     </row>
     <row r="16">
@@ -1334,55 +1339,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.06904480083364965</v>
+        <v>-0.06902181566263875</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.2013233581676131</v>
+        <v>-0.2013189267638788</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2573427440388361</v>
+        <v>-0.2573533126466964</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.205213775179221</v>
+        <v>-0.205251616984405</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2839238188430767</v>
+        <v>-0.2839049258083452</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1126902402387405</v>
+        <v>-0.1126794381419477</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06998007005675233</v>
+        <v>0.06997282380626559</v>
       </c>
       <c r="I16" t="n">
-        <v>0.124079746024738</v>
+        <v>0.124056244371458</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1713143559026086</v>
+        <v>0.1712780086623092</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1606303868978582</v>
+        <v>-0.1606870530328374</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2148822246209863</v>
+        <v>-0.2148776531625478</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1366015913251175</v>
+        <v>0.136572932472734</v>
       </c>
       <c r="N16" t="n">
-        <v>0.04611701743477972</v>
+        <v>0.04613873483677771</v>
       </c>
       <c r="O16" t="n">
-        <v>0.109614919639041</v>
+        <v>0.1096078040842981</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.04613179990092944</v>
+        <v>0.04611673134781093</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.06344557580638711</v>
+        <v>-0.0634642654125918</v>
       </c>
     </row>
     <row r="17">
@@ -1392,55 +1397,55 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2385553216662413</v>
+        <v>0.2385784067744992</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.2856321845897071</v>
+        <v>-0.2856150608309959</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2489369253156401</v>
+        <v>-0.2489262478488573</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2016406696038461</v>
+        <v>-0.2016478065199879</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3191799752794228</v>
+        <v>-0.3191443600895812</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09661437986647123</v>
+        <v>0.09663939489526456</v>
       </c>
       <c r="H17" t="n">
-        <v>0.08893520048610355</v>
+        <v>0.08893469340784468</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09159705332043251</v>
+        <v>0.09157803497197814</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.16482181116206</v>
+        <v>-0.1648444999658344</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.09964985837325757</v>
+        <v>-0.09967136712906929</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1535565692291639</v>
+        <v>-0.1535368865708304</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1719026519760143</v>
+        <v>0.1719004039390848</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1962577232960025</v>
+        <v>-0.1962583371125046</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.07527496955582919</v>
+        <v>-0.07527595497036675</v>
       </c>
       <c r="P17" t="n">
-        <v>0.04613179990092944</v>
+        <v>0.04611673134781093</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1225046703727761</v>
+        <v>0.1225049463706882</v>
       </c>
     </row>
     <row r="18">
@@ -1450,52 +1455,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.05405983917825068</v>
+        <v>-0.0540390569466519</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01665625854247623</v>
+        <v>0.01666186926508546</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1334469483901256</v>
+        <v>-0.1334446568452315</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.07209876631395257</v>
+        <v>-0.07210677558561417</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.01837612761457592</v>
+        <v>-0.01835019132009135</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1196309482847191</v>
+        <v>-0.1196118101964955</v>
       </c>
       <c r="H18" t="n">
-        <v>0.02723473760500227</v>
+        <v>0.02723415946797429</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1366922402025685</v>
+        <v>-0.1367166683597793</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1053417684692502</v>
+        <v>-0.1053678463581126</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2121871143928384</v>
+        <v>-0.212209981122964</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.07797808616199489</v>
+        <v>-0.07796446988769261</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.03703553495467672</v>
+        <v>-0.03703934509560883</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2627404681404036</v>
+        <v>-0.2627390228657359</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1390574325133239</v>
+        <v>-0.1390671331264856</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.06344557580638711</v>
+        <v>-0.0634642654125918</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1225046703727761</v>
+        <v>0.1225049463706882</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
